--- a/exemples/exemple-import.xlsx
+++ b/exemples/exemple-import.xlsx
@@ -789,11 +789,11 @@
       <c r="R5" t="str">
         <v/>
       </c>
-      <c r="S5" t="str">
-        <v/>
-      </c>
-      <c r="T5" t="str">
-        <v/>
+      <c r="S5">
+        <v>210000</v>
+      </c>
+      <c r="T5">
+        <v>200000</v>
       </c>
       <c r="U5" t="str">
         <v/>
@@ -1003,11 +1003,11 @@
       <c r="R7" t="str">
         <v/>
       </c>
-      <c r="S7" t="str">
-        <v/>
-      </c>
-      <c r="T7" t="str">
-        <v/>
+      <c r="S7">
+        <v>95000</v>
+      </c>
+      <c r="T7">
+        <v>180000</v>
       </c>
       <c r="U7" t="str">
         <v/>
@@ -1110,11 +1110,11 @@
       <c r="R8" t="str">
         <v/>
       </c>
-      <c r="S8" t="str">
-        <v/>
-      </c>
-      <c r="T8" t="str">
-        <v/>
+      <c r="S8">
+        <v>260000</v>
+      </c>
+      <c r="T8">
+        <v>200000</v>
       </c>
       <c r="U8" t="str">
         <v/>
@@ -1217,11 +1217,11 @@
       <c r="R9" t="str">
         <v/>
       </c>
-      <c r="S9" t="str">
-        <v/>
-      </c>
-      <c r="T9" t="str">
-        <v/>
+      <c r="S9">
+        <v>60000</v>
+      </c>
+      <c r="T9">
+        <v>140000</v>
       </c>
       <c r="U9" t="str">
         <v/>
@@ -1324,11 +1324,11 @@
       <c r="R10" t="str">
         <v/>
       </c>
-      <c r="S10" t="str">
-        <v/>
-      </c>
-      <c r="T10" t="str">
-        <v/>
+      <c r="S10">
+        <v>150000</v>
+      </c>
+      <c r="T10">
+        <v>160000</v>
       </c>
       <c r="U10" t="str">
         <v/>
@@ -1651,11 +1651,11 @@
       <c r="T14" t="str">
         <v/>
       </c>
-      <c r="U14" t="str">
-        <v/>
-      </c>
-      <c r="V14" t="str">
-        <v/>
+      <c r="U14">
+        <v>70000</v>
+      </c>
+      <c r="V14">
+        <v>60000</v>
       </c>
       <c r="W14" t="str">
         <v/>
@@ -1758,11 +1758,11 @@
       <c r="T15" t="str">
         <v/>
       </c>
-      <c r="U15" t="str">
-        <v/>
-      </c>
-      <c r="V15" t="str">
-        <v/>
+      <c r="U15">
+        <v>30000</v>
+      </c>
+      <c r="V15">
+        <v>65000</v>
       </c>
       <c r="W15" t="str">
         <v/>
@@ -1865,11 +1865,11 @@
       <c r="T16" t="str">
         <v/>
       </c>
-      <c r="U16" t="str">
-        <v/>
-      </c>
-      <c r="V16" t="str">
-        <v/>
+      <c r="U16">
+        <v>55000</v>
+      </c>
+      <c r="V16">
+        <v>70000</v>
       </c>
       <c r="W16" t="str">
         <v/>
@@ -1972,11 +1972,11 @@
       <c r="T17" t="str">
         <v/>
       </c>
-      <c r="U17" t="str">
-        <v/>
-      </c>
-      <c r="V17" t="str">
-        <v/>
+      <c r="U17">
+        <v>98000</v>
+      </c>
+      <c r="V17">
+        <v>80000</v>
       </c>
       <c r="W17" t="str">
         <v/>
@@ -2299,11 +2299,11 @@
       <c r="V20" t="str">
         <v/>
       </c>
-      <c r="W20" t="str">
-        <v/>
-      </c>
-      <c r="X20" t="str">
-        <v/>
+      <c r="W20">
+        <v>45000</v>
+      </c>
+      <c r="X20">
+        <v>50000</v>
       </c>
       <c r="Y20" t="str">
         <v/>
@@ -2519,11 +2519,11 @@
       <c r="X22" t="str">
         <v/>
       </c>
-      <c r="Y22" t="str">
-        <v/>
-      </c>
-      <c r="Z22" t="str">
-        <v/>
+      <c r="Y22">
+        <v>20000</v>
+      </c>
+      <c r="Z22">
+        <v>25000</v>
       </c>
       <c r="AA22" t="str">
         <v/>

--- a/exemples/exemple-import.xlsx
+++ b/exemples/exemple-import.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AK23"/>
   <cols>
     <col min="1" max="1" width="2.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -427,6 +427,8 @@
     <col min="24" max="24" width="12.83203125" customWidth="1"/>
     <col min="25" max="25" width="12.83203125" customWidth="1"/>
     <col min="26" max="26" width="12.83203125" customWidth="1"/>
+    <col min="27" max="27" width="12.83203125" customWidth="1"/>
+    <col min="28" max="28" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -600,30 +602,36 @@
         <v>Objectif BK</v>
       </c>
       <c r="AA3" t="str">
-        <v/>
+        <v>Téléphone</v>
       </c>
       <c r="AB3" t="str">
+        <v>E-mail</v>
+      </c>
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
         <v>Commercial</v>
       </c>
-      <c r="AC3" t="str">
+      <c r="AE3" t="str">
         <v>Structure</v>
       </c>
-      <c r="AD3" t="str">
+      <c r="AF3" t="str">
         <v>Dépt</v>
       </c>
-      <c r="AE3" t="str">
+      <c r="AG3" t="str">
         <v>Arr.</v>
       </c>
-      <c r="AF3" t="str">
+      <c r="AH3" t="str">
         <v>Couverture</v>
       </c>
-      <c r="AG3" t="str">
+      <c r="AI3" t="str">
         <v>Manager 1</v>
       </c>
-      <c r="AH3" t="str">
+      <c r="AJ3" t="str">
         <v>Manager 2</v>
       </c>
-      <c r="AI3" t="str">
+      <c r="AK3" t="str">
         <v>Statut</v>
       </c>
     </row>
@@ -707,30 +715,36 @@
         <v/>
       </c>
       <c r="AA4" t="str">
-        <v/>
+        <v>0639980001</v>
       </c>
       <c r="AB4" t="str">
+        <v>Agathe.Rolland@Example.com</v>
+      </c>
+      <c r="AC4" t="str">
+        <v/>
+      </c>
+      <c r="AD4" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC4" t="str">
+      <c r="AE4" t="str">
         <v>MD</v>
       </c>
-      <c r="AD4" t="str">
+      <c r="AF4" t="str">
         <v>29</v>
       </c>
-      <c r="AE4" t="str">
-        <v/>
-      </c>
-      <c r="AF4" t="str">
+      <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG4" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH4" t="str">
+      <c r="AI4" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ4" t="str">
         <v>Y</v>
       </c>
-      <c r="AI4" t="str">
+      <c r="AK4" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -814,30 +828,36 @@
         <v/>
       </c>
       <c r="AA5" t="str">
-        <v/>
+        <v>06.39.98.00.02</v>
       </c>
       <c r="AB5" t="str">
+        <v>basile.fournier@example.com</v>
+      </c>
+      <c r="AC5" t="str">
+        <v/>
+      </c>
+      <c r="AD5" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC5" t="str">
+      <c r="AE5" t="str">
         <v>MD</v>
       </c>
-      <c r="AD5" t="str">
+      <c r="AF5" t="str">
         <v>29</v>
       </c>
-      <c r="AE5" t="str">
-        <v/>
-      </c>
-      <c r="AF5" t="str">
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG5" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH5" t="str">
+      <c r="AI5" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ5" t="str">
         <v>Y</v>
       </c>
-      <c r="AI5" t="str">
+      <c r="AK5" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -921,30 +941,36 @@
         <v/>
       </c>
       <c r="AA6" t="str">
-        <v/>
+        <v>+33 6 39 98 00 03</v>
       </c>
       <c r="AB6" t="str">
+        <v>capucine.delorme@example.com</v>
+      </c>
+      <c r="AC6" t="str">
+        <v/>
+      </c>
+      <c r="AD6" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC6" t="str">
+      <c r="AE6" t="str">
         <v>MD</v>
       </c>
-      <c r="AD6" t="str">
+      <c r="AF6" t="str">
         <v>29</v>
       </c>
-      <c r="AE6" t="str">
-        <v/>
-      </c>
-      <c r="AF6" t="str">
+      <c r="AG6" t="str">
+        <v/>
+      </c>
+      <c r="AH6" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG6" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH6" t="str">
+      <c r="AI6" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ6" t="str">
         <v>Y</v>
       </c>
-      <c r="AI6" t="str">
+      <c r="AK6" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -1027,31 +1053,37 @@
       <c r="Z7" t="str">
         <v/>
       </c>
-      <c r="AA7" t="str">
-        <v/>
+      <c r="AA7">
+        <v>639980004</v>
       </c>
       <c r="AB7" t="str">
+        <v>dorian.marchal@example.com</v>
+      </c>
+      <c r="AC7" t="str">
+        <v/>
+      </c>
+      <c r="AD7" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC7" t="str">
+      <c r="AE7" t="str">
         <v>MD</v>
       </c>
-      <c r="AD7" t="str">
+      <c r="AF7" t="str">
         <v>29</v>
       </c>
-      <c r="AE7" t="str">
-        <v/>
-      </c>
-      <c r="AF7" t="str">
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG7" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH7" t="str">
+      <c r="AI7" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ7" t="str">
         <v>Y</v>
       </c>
-      <c r="AI7" t="str">
+      <c r="AK7" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -1135,30 +1167,36 @@
         <v/>
       </c>
       <c r="AA8" t="str">
-        <v/>
+        <v>06 39 98 00 05</v>
       </c>
       <c r="AB8" t="str">
+        <v>elodie.vasseur@example.com</v>
+      </c>
+      <c r="AC8" t="str">
+        <v/>
+      </c>
+      <c r="AD8" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC8" t="str">
+      <c r="AE8" t="str">
         <v>MD</v>
       </c>
-      <c r="AD8" t="str">
+      <c r="AF8" t="str">
         <v>29</v>
       </c>
-      <c r="AE8" t="str">
-        <v/>
-      </c>
-      <c r="AF8" t="str">
+      <c r="AG8" t="str">
+        <v/>
+      </c>
+      <c r="AH8" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG8" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH8" t="str">
+      <c r="AI8" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ8" t="str">
         <v>Y</v>
       </c>
-      <c r="AI8" t="str">
+      <c r="AK8" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -1242,30 +1280,36 @@
         <v/>
       </c>
       <c r="AA9" t="str">
-        <v/>
+        <v>06 39 98 00 06</v>
       </c>
       <c r="AB9" t="str">
+        <v/>
+      </c>
+      <c r="AC9" t="str">
+        <v/>
+      </c>
+      <c r="AD9" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC9" t="str">
+      <c r="AE9" t="str">
         <v>MD</v>
       </c>
-      <c r="AD9" t="str">
+      <c r="AF9" t="str">
         <v>29</v>
       </c>
-      <c r="AE9" t="str">
-        <v/>
-      </c>
-      <c r="AF9" t="str">
+      <c r="AG9" t="str">
+        <v/>
+      </c>
+      <c r="AH9" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG9" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH9" t="str">
+      <c r="AI9" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ9" t="str">
         <v>Y</v>
       </c>
-      <c r="AI9" t="str">
+      <c r="AK9" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -1352,27 +1396,33 @@
         <v/>
       </c>
       <c r="AB10" t="str">
+        <v/>
+      </c>
+      <c r="AC10" t="str">
+        <v/>
+      </c>
+      <c r="AD10" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC10" t="str">
+      <c r="AE10" t="str">
         <v>MD</v>
       </c>
-      <c r="AD10" t="str">
+      <c r="AF10" t="str">
         <v>29</v>
       </c>
-      <c r="AE10" t="str">
-        <v/>
-      </c>
-      <c r="AF10" t="str">
+      <c r="AG10" t="str">
+        <v/>
+      </c>
+      <c r="AH10" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG10" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH10" t="str">
+      <c r="AI10" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ10" t="str">
         <v>Y</v>
       </c>
-      <c r="AI10" t="str">
+      <c r="AK10" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -1459,27 +1509,33 @@
         <v/>
       </c>
       <c r="AB12" t="str">
+        <v/>
+      </c>
+      <c r="AC12" t="str">
+        <v/>
+      </c>
+      <c r="AD12" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC12" t="str">
+      <c r="AE12" t="str">
         <v>MD</v>
       </c>
-      <c r="AD12" t="str">
+      <c r="AF12" t="str">
         <v>29</v>
       </c>
-      <c r="AE12" t="str">
-        <v/>
-      </c>
-      <c r="AF12" t="str">
+      <c r="AG12" t="str">
+        <v/>
+      </c>
+      <c r="AH12" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG12" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH12" t="str">
+      <c r="AI12" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ12" t="str">
         <v>Y</v>
       </c>
-      <c r="AI12" t="str">
+      <c r="AK12" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -1566,27 +1622,33 @@
         <v/>
       </c>
       <c r="AB13" t="str">
+        <v/>
+      </c>
+      <c r="AC13" t="str">
+        <v/>
+      </c>
+      <c r="AD13" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC13" t="str">
+      <c r="AE13" t="str">
         <v>MD</v>
       </c>
-      <c r="AD13" t="str">
+      <c r="AF13" t="str">
         <v>29</v>
       </c>
-      <c r="AE13" t="str">
-        <v/>
-      </c>
-      <c r="AF13" t="str">
+      <c r="AG13" t="str">
+        <v/>
+      </c>
+      <c r="AH13" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG13" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH13" t="str">
+      <c r="AI13" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ13" t="str">
         <v>Y</v>
       </c>
-      <c r="AI13" t="str">
+      <c r="AK13" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -1670,30 +1732,36 @@
         <v/>
       </c>
       <c r="AA14" t="str">
-        <v/>
+        <v>06 39 98 00 11</v>
       </c>
       <c r="AB14" t="str">
+        <v>leonie.hamon@example.com</v>
+      </c>
+      <c r="AC14" t="str">
+        <v/>
+      </c>
+      <c r="AD14" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC14" t="str">
+      <c r="AE14" t="str">
         <v>MD</v>
       </c>
-      <c r="AD14" t="str">
+      <c r="AF14" t="str">
         <v>29</v>
       </c>
-      <c r="AE14" t="str">
-        <v/>
-      </c>
-      <c r="AF14" t="str">
+      <c r="AG14" t="str">
+        <v/>
+      </c>
+      <c r="AH14" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG14" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH14" t="str">
+      <c r="AI14" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ14" t="str">
         <v>Y</v>
       </c>
-      <c r="AI14" t="str">
+      <c r="AK14" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -1780,27 +1848,33 @@
         <v/>
       </c>
       <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <v/>
+      </c>
+      <c r="AD15" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC15" t="str">
+      <c r="AE15" t="str">
         <v>MD</v>
       </c>
-      <c r="AD15" t="str">
+      <c r="AF15" t="str">
         <v>29</v>
       </c>
-      <c r="AE15" t="str">
-        <v/>
-      </c>
-      <c r="AF15" t="str">
+      <c r="AG15" t="str">
+        <v/>
+      </c>
+      <c r="AH15" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG15" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH15" t="str">
+      <c r="AI15" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ15" t="str">
         <v>Y</v>
       </c>
-      <c r="AI15" t="str">
+      <c r="AK15" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -1887,27 +1961,33 @@
         <v/>
       </c>
       <c r="AB16" t="str">
+        <v/>
+      </c>
+      <c r="AC16" t="str">
+        <v/>
+      </c>
+      <c r="AD16" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC16" t="str">
+      <c r="AE16" t="str">
         <v>MD</v>
       </c>
-      <c r="AD16" t="str">
+      <c r="AF16" t="str">
         <v>29</v>
       </c>
-      <c r="AE16" t="str">
-        <v/>
-      </c>
-      <c r="AF16" t="str">
+      <c r="AG16" t="str">
+        <v/>
+      </c>
+      <c r="AH16" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG16" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH16" t="str">
+      <c r="AI16" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ16" t="str">
         <v>Y</v>
       </c>
-      <c r="AI16" t="str">
+      <c r="AK16" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -1994,27 +2074,33 @@
         <v/>
       </c>
       <c r="AB17" t="str">
+        <v>simon.kervella@example.com</v>
+      </c>
+      <c r="AC17" t="str">
+        <v/>
+      </c>
+      <c r="AD17" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC17" t="str">
+      <c r="AE17" t="str">
         <v>MD</v>
       </c>
-      <c r="AD17" t="str">
+      <c r="AF17" t="str">
         <v>29</v>
       </c>
-      <c r="AE17" t="str">
-        <v/>
-      </c>
-      <c r="AF17" t="str">
+      <c r="AG17" t="str">
+        <v/>
+      </c>
+      <c r="AH17" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG17" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH17" t="str">
+      <c r="AI17" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ17" t="str">
         <v>Y</v>
       </c>
-      <c r="AI17" t="str">
+      <c r="AK17" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -2101,27 +2187,33 @@
         <v/>
       </c>
       <c r="AB18" t="str">
+        <v/>
+      </c>
+      <c r="AC18" t="str">
+        <v/>
+      </c>
+      <c r="AD18" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC18" t="str">
+      <c r="AE18" t="str">
         <v>MD</v>
       </c>
-      <c r="AD18" t="str">
+      <c r="AF18" t="str">
         <v>29</v>
       </c>
-      <c r="AE18" t="str">
-        <v/>
-      </c>
-      <c r="AF18" t="str">
+      <c r="AG18" t="str">
+        <v/>
+      </c>
+      <c r="AH18" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG18" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH18" t="str">
+      <c r="AI18" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ18" t="str">
         <v>Y</v>
       </c>
-      <c r="AI18" t="str">
+      <c r="AK18" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -2208,27 +2300,33 @@
         <v/>
       </c>
       <c r="AB19" t="str">
+        <v/>
+      </c>
+      <c r="AC19" t="str">
+        <v/>
+      </c>
+      <c r="AD19" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC19" t="str">
+      <c r="AE19" t="str">
         <v>MD</v>
       </c>
-      <c r="AD19" t="str">
+      <c r="AF19" t="str">
         <v>29</v>
       </c>
-      <c r="AE19" t="str">
-        <v/>
-      </c>
-      <c r="AF19" t="str">
+      <c r="AG19" t="str">
+        <v/>
+      </c>
+      <c r="AH19" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG19" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH19" t="str">
+      <c r="AI19" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ19" t="str">
         <v>Y</v>
       </c>
-      <c r="AI19" t="str">
+      <c r="AK19" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -2315,27 +2413,33 @@
         <v/>
       </c>
       <c r="AB20" t="str">
+        <v/>
+      </c>
+      <c r="AC20" t="str">
+        <v/>
+      </c>
+      <c r="AD20" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC20" t="str">
+      <c r="AE20" t="str">
         <v>MD</v>
       </c>
-      <c r="AD20" t="str">
+      <c r="AF20" t="str">
         <v>29</v>
       </c>
-      <c r="AE20" t="str">
-        <v/>
-      </c>
-      <c r="AF20" t="str">
+      <c r="AG20" t="str">
+        <v/>
+      </c>
+      <c r="AH20" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG20" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH20" t="str">
+      <c r="AI20" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ20" t="str">
         <v>Y</v>
       </c>
-      <c r="AI20" t="str">
+      <c r="AK20" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -2422,27 +2526,33 @@
         <v/>
       </c>
       <c r="AB21" t="str">
+        <v/>
+      </c>
+      <c r="AC21" t="str">
+        <v/>
+      </c>
+      <c r="AD21" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC21" t="str">
+      <c r="AE21" t="str">
         <v>MD</v>
       </c>
-      <c r="AD21" t="str">
+      <c r="AF21" t="str">
         <v>29</v>
       </c>
-      <c r="AE21" t="str">
-        <v/>
-      </c>
-      <c r="AF21" t="str">
+      <c r="AG21" t="str">
+        <v/>
+      </c>
+      <c r="AH21" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG21" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH21" t="str">
+      <c r="AI21" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ21" t="str">
         <v>Y</v>
       </c>
-      <c r="AI21" t="str">
+      <c r="AK21" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -2526,30 +2636,36 @@
         <v>25000</v>
       </c>
       <c r="AA22" t="str">
-        <v/>
+        <v>06 39 98 00 21</v>
       </c>
       <c r="AB22" t="str">
+        <v>jade.pradel@example.com</v>
+      </c>
+      <c r="AC22" t="str">
+        <v/>
+      </c>
+      <c r="AD22" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC22" t="str">
+      <c r="AE22" t="str">
         <v>MD</v>
       </c>
-      <c r="AD22" t="str">
+      <c r="AF22" t="str">
         <v>29</v>
       </c>
-      <c r="AE22" t="str">
-        <v/>
-      </c>
-      <c r="AF22" t="str">
+      <c r="AG22" t="str">
+        <v/>
+      </c>
+      <c r="AH22" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG22" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH22" t="str">
+      <c r="AI22" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ22" t="str">
         <v>Y</v>
       </c>
-      <c r="AI22" t="str">
+      <c r="AK22" t="str">
         <v>VRP</v>
       </c>
     </row>
@@ -2636,33 +2752,39 @@
         <v/>
       </c>
       <c r="AB23" t="str">
+        <v/>
+      </c>
+      <c r="AC23" t="str">
+        <v/>
+      </c>
+      <c r="AD23" t="str">
         <v>calcul</v>
       </c>
-      <c r="AC23" t="str">
+      <c r="AE23" t="str">
         <v>MD</v>
       </c>
-      <c r="AD23" t="str">
+      <c r="AF23" t="str">
         <v>29</v>
       </c>
-      <c r="AE23" t="str">
-        <v/>
-      </c>
-      <c r="AF23" t="str">
+      <c r="AG23" t="str">
+        <v/>
+      </c>
+      <c r="AH23" t="str">
         <v>Propre</v>
       </c>
-      <c r="AG23" t="str">
-        <v>X</v>
-      </c>
-      <c r="AH23" t="str">
+      <c r="AI23" t="str">
+        <v>X</v>
+      </c>
+      <c r="AJ23" t="str">
         <v>Y</v>
       </c>
-      <c r="AI23" t="str">
+      <c r="AK23" t="str">
         <v>VRP</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AI23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AK23"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/exemples/exemple-import.xlsx
+++ b/exemples/exemple-import.xlsx
@@ -1583,7 +1583,7 @@
         <v>Secteur Centre</v>
       </c>
       <c r="O13" t="str">
-        <v>18, 36, 41, 45</v>
+        <v>18, 36P, 41, 45</v>
       </c>
       <c r="P13" t="str">
         <v/>
@@ -1925,7 +1925,7 @@
         <v/>
       </c>
       <c r="P16" t="str">
-        <v>07G, 26G, 48P, 30</v>
+        <v>07GP, 26G, 48P, 30</v>
       </c>
       <c r="Q16" t="str">
         <v/>
